--- a/tests/testdata/testdata_multiple_values_multiple_sheets.xlsx
+++ b/tests/testdata/testdata_multiple_values_multiple_sheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\jef\repositories\gitea\foz\mango-metadata-from-tables\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mariana\repos\gitea\foz\mango-metadata-from-tables\tests\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE6395D-B326-4F26-B953-61570747C226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BB6C0F-2DA0-44E3-B30C-8E8202958DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{844CE011-18D6-43C8-8FB7-98638B60225B}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{844CE011-18D6-43C8-8FB7-98638B60225B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
     <t>author</t>
   </si>
   <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file1.txt</t>
-  </si>
-  <si>
     <t>shape</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>heart</t>
   </si>
   <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file2.txt</t>
-  </si>
-  <si>
     <t>big</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
     <t>square</t>
   </si>
   <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file3.txt</t>
-  </si>
-  <si>
     <t>Jane Doe;Fulano De Tal</t>
   </si>
   <si>
@@ -108,13 +99,22 @@
     <t>purple</t>
   </si>
   <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file4.txt</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
     <t>This is a text with a colon ; but it should not be split</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file4.txt</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file3.txt</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file1.txt</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file2.txt</t>
   </si>
 </sst>
 </file>
@@ -487,9 +487,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72194BE-5A13-4ACF-9495-1A02F8B90294}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="67.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,58 +506,58 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -565,9 +568,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB41108C-DC50-47DA-B591-1767531EDF0E}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="67.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -581,30 +587,30 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
